--- a/resources/Protocol.xlsx
+++ b/resources/Protocol.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Documents\Visual Studio Code\Psychopy\Parallel learning\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\experiments programming\template psychojs\coriumgit.github.io\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAA0A96-ACAB-4890-85C1-1A5CC784EF2F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3386DA39-DEF2-4DCE-9E55-9BE3996D207C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,8 +75,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -358,10 +359,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.59765625" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
@@ -371,280 +375,280 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>41324</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>41324</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>41324</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>41324</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>41324</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>41324</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>41324</v>
       </c>
       <c r="C8">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>41324</v>
       </c>
       <c r="C9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>41324</v>
       </c>
       <c r="C10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>41324</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>41324</v>
       </c>
       <c r="C12">
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>42314</v>
       </c>
       <c r="C13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>42314</v>
       </c>
       <c r="C14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>42314</v>
       </c>
       <c r="C15">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>42314</v>
       </c>
       <c r="C16">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>42314</v>
       </c>
       <c r="C17">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>42314</v>
       </c>
       <c r="C18">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>42314</v>
       </c>
       <c r="C19">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>42314</v>
       </c>
       <c r="C20">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>42314</v>
       </c>
       <c r="C21">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>42314</v>
       </c>
       <c r="C22">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>42314</v>
       </c>
       <c r="C23">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>42314</v>
       </c>
       <c r="C24">
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>23142</v>
       </c>
       <c r="C25">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>23142</v>
       </c>
       <c r="C26">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>23142</v>
       </c>
       <c r="C27">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>23142</v>
       </c>
       <c r="C28">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>23142</v>
       </c>
       <c r="C29">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>23142</v>
       </c>
       <c r="C30">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>23142</v>
       </c>
       <c r="C31">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>23142</v>
       </c>
       <c r="C32">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>23142</v>
       </c>
       <c r="C33">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>23142</v>
       </c>
       <c r="C34">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>23142</v>
       </c>
       <c r="C35">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>23142</v>
       </c>
       <c r="C36">
@@ -654,5 +658,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/resources/Protocol.xlsx
+++ b/resources/Protocol.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\experiments programming\template psychojs\coriumgit.github.io\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3386DA39-DEF2-4DCE-9E55-9BE3996D207C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1337F339-FD2D-4017-97AA-8AE52FD848A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,7 +358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.59765625" style="1" customWidth="1"/>
@@ -380,23 +380,23 @@
         <v>41324</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>41324</v>
+        <v>42314</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>41324</v>
+        <v>42314</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -404,7 +404,7 @@
         <v>41324</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -412,248 +412,11 @@
         <v>41324</v>
       </c>
       <c r="C6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>41324</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>41324</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>41324</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>41324</v>
-      </c>
-      <c r="C10">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>41324</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>41324</v>
-      </c>
-      <c r="C12">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C24">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C27">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C29">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C30">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C31">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C32">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C33">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C34">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>23142</v>
-      </c>
-      <c r="C36">
-        <v>10</v>
-      </c>
+      <c r="A11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/resources/Protocol.xlsx
+++ b/resources/Protocol.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\experiments programming\template psychojs\coriumgit.github.io\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1337F339-FD2D-4017-97AA-8AE52FD848A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A333AD-5891-4F02-9C19-BA98D243F4C9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,30 +391,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>42314</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>41324</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>41324</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-    </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11"/>
     </row>
